--- a/HelloFresh_Absorption.xlsx
+++ b/HelloFresh_Absorption.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://nuwildcat-my.sharepoint.com/personal/stn424_ads_northwestern_edu/Documents/Collaborations/Proposals/GO-Barrier, TFMI Proposals with Tim Wei/URAP_2023-10/Shared/Lanning, Mackenzie/Absorption Data/Fall 2025/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://nuwildcat-my.sharepoint.com/personal/stn424_ads_northwestern_edu/Documents/Collaborations/Proposals/GO-Barrier, TFMI Proposals with Tim Wei/URAP_2023-10/Shared/Lanning, Mackenzie/graphene-oxide-paper-coatings/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="2134" documentId="13_ncr:1_{F2E763B4-4DB6-894B-B240-8188D6068E1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{86EF033D-2D68-2D4E-9CB9-4B2F3C23BAA6}"/>
   <bookViews>
-    <workbookView xWindow="13980" yWindow="740" windowWidth="15420" windowHeight="17180" firstSheet="1" activeTab="5" xr2:uid="{304DC28A-0BB6-064B-B35E-217EA1A1C90F}"/>
+    <workbookView xWindow="13980" yWindow="740" windowWidth="15420" windowHeight="17180" firstSheet="2" activeTab="6" xr2:uid="{304DC28A-0BB6-064B-B35E-217EA1A1C90F}"/>
   </bookViews>
   <sheets>
     <sheet name="Crayola Method" sheetId="1" r:id="rId1"/>
@@ -373,14 +373,14 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -32320,24 +32320,24 @@
       <c r="P1" s="3"/>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A2" s="29" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="29"/>
-      <c r="C2" s="29"/>
-      <c r="D2" s="29"/>
-      <c r="E2" s="29"/>
-      <c r="F2" s="29"/>
-      <c r="G2" s="29"/>
-      <c r="H2" s="29"/>
-      <c r="I2" s="29"/>
-      <c r="J2" s="29"/>
-      <c r="K2" s="29"/>
-      <c r="L2" s="29"/>
-      <c r="M2" s="29"/>
-      <c r="N2" s="29"/>
-      <c r="O2" s="29"/>
-      <c r="P2" s="29"/>
+      <c r="A2" s="30" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="30"/>
+      <c r="C2" s="30"/>
+      <c r="D2" s="30"/>
+      <c r="E2" s="30"/>
+      <c r="F2" s="30"/>
+      <c r="G2" s="30"/>
+      <c r="H2" s="30"/>
+      <c r="I2" s="30"/>
+      <c r="J2" s="30"/>
+      <c r="K2" s="30"/>
+      <c r="L2" s="30"/>
+      <c r="M2" s="30"/>
+      <c r="N2" s="30"/>
+      <c r="O2" s="30"/>
+      <c r="P2" s="30"/>
     </row>
     <row r="3" spans="1:18" ht="51" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
@@ -34282,24 +34282,24 @@
       <c r="P46" s="5"/>
     </row>
     <row r="47" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A47" s="30" t="s">
+      <c r="A47" s="31" t="s">
         <v>3</v>
       </c>
-      <c r="B47" s="30"/>
-      <c r="C47" s="30"/>
-      <c r="D47" s="30"/>
-      <c r="E47" s="30"/>
-      <c r="F47" s="30"/>
-      <c r="G47" s="30"/>
-      <c r="H47" s="30"/>
-      <c r="I47" s="30"/>
-      <c r="J47" s="30"/>
-      <c r="K47" s="30"/>
-      <c r="L47" s="30"/>
-      <c r="M47" s="30"/>
-      <c r="N47" s="30"/>
-      <c r="O47" s="30"/>
-      <c r="P47" s="30"/>
+      <c r="B47" s="31"/>
+      <c r="C47" s="31"/>
+      <c r="D47" s="31"/>
+      <c r="E47" s="31"/>
+      <c r="F47" s="31"/>
+      <c r="G47" s="31"/>
+      <c r="H47" s="31"/>
+      <c r="I47" s="31"/>
+      <c r="J47" s="31"/>
+      <c r="K47" s="31"/>
+      <c r="L47" s="31"/>
+      <c r="M47" s="31"/>
+      <c r="N47" s="31"/>
+      <c r="O47" s="31"/>
+      <c r="P47" s="31"/>
     </row>
     <row r="48" spans="1:16" ht="51" x14ac:dyDescent="0.2">
       <c r="A48" s="2" t="s">
@@ -38665,13 +38665,13 @@
       <c r="H1" s="2"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A2" s="29" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="29"/>
-      <c r="C2" s="29"/>
-      <c r="D2" s="29"/>
-      <c r="E2" s="29"/>
+      <c r="A2" s="30" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="30"/>
+      <c r="C2" s="30"/>
+      <c r="D2" s="30"/>
+      <c r="E2" s="30"/>
       <c r="F2" s="2"/>
       <c r="G2" s="2"/>
       <c r="H2" s="2"/>
@@ -39839,13 +39839,13 @@
       <c r="H52" s="4"/>
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A53" s="30" t="s">
+      <c r="A53" s="31" t="s">
         <v>3</v>
       </c>
-      <c r="B53" s="30"/>
-      <c r="C53" s="30"/>
-      <c r="D53" s="30"/>
-      <c r="E53" s="30"/>
+      <c r="B53" s="31"/>
+      <c r="C53" s="31"/>
+      <c r="D53" s="31"/>
+      <c r="E53" s="31"/>
       <c r="F53" s="2"/>
       <c r="G53" s="2"/>
       <c r="H53" s="2"/>
@@ -43007,13 +43007,13 @@
       <c r="H1" s="2"/>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A2" s="29" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="29"/>
-      <c r="C2" s="29"/>
-      <c r="D2" s="29"/>
-      <c r="E2" s="29"/>
+      <c r="A2" s="30" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="30"/>
+      <c r="C2" s="30"/>
+      <c r="D2" s="30"/>
+      <c r="E2" s="30"/>
       <c r="F2" s="2"/>
       <c r="G2" s="2"/>
       <c r="H2" s="2"/>
@@ -44933,13 +44933,13 @@
       <c r="R52" s="5"/>
     </row>
     <row r="53" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A53" s="30" t="s">
+      <c r="A53" s="31" t="s">
         <v>3</v>
       </c>
-      <c r="B53" s="30"/>
-      <c r="C53" s="30"/>
-      <c r="D53" s="30"/>
-      <c r="E53" s="30"/>
+      <c r="B53" s="31"/>
+      <c r="C53" s="31"/>
+      <c r="D53" s="31"/>
+      <c r="E53" s="31"/>
       <c r="F53" s="2"/>
       <c r="G53" s="2"/>
       <c r="H53" s="2"/>
@@ -49894,24 +49894,24 @@
       <c r="P1" s="3"/>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A2" s="29" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="29"/>
-      <c r="C2" s="29"/>
-      <c r="D2" s="29"/>
-      <c r="E2" s="29"/>
-      <c r="F2" s="29"/>
-      <c r="G2" s="29"/>
-      <c r="H2" s="29"/>
-      <c r="I2" s="29"/>
-      <c r="J2" s="29"/>
-      <c r="K2" s="29"/>
-      <c r="L2" s="29"/>
-      <c r="M2" s="29"/>
-      <c r="N2" s="29"/>
-      <c r="O2" s="29"/>
-      <c r="P2" s="29"/>
+      <c r="A2" s="30" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="30"/>
+      <c r="C2" s="30"/>
+      <c r="D2" s="30"/>
+      <c r="E2" s="30"/>
+      <c r="F2" s="30"/>
+      <c r="G2" s="30"/>
+      <c r="H2" s="30"/>
+      <c r="I2" s="30"/>
+      <c r="J2" s="30"/>
+      <c r="K2" s="30"/>
+      <c r="L2" s="30"/>
+      <c r="M2" s="30"/>
+      <c r="N2" s="30"/>
+      <c r="O2" s="30"/>
+      <c r="P2" s="30"/>
     </row>
     <row r="3" spans="1:16" ht="34" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
@@ -51138,24 +51138,24 @@
       <c r="P46" s="5"/>
     </row>
     <row r="47" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A47" s="30" t="s">
+      <c r="A47" s="31" t="s">
         <v>3</v>
       </c>
-      <c r="B47" s="30"/>
-      <c r="C47" s="30"/>
-      <c r="D47" s="30"/>
-      <c r="E47" s="30"/>
-      <c r="F47" s="30"/>
-      <c r="G47" s="30"/>
-      <c r="H47" s="30"/>
-      <c r="I47" s="30"/>
-      <c r="J47" s="30"/>
-      <c r="K47" s="30"/>
-      <c r="L47" s="30"/>
-      <c r="M47" s="30"/>
-      <c r="N47" s="30"/>
-      <c r="O47" s="30"/>
-      <c r="P47" s="30"/>
+      <c r="B47" s="31"/>
+      <c r="C47" s="31"/>
+      <c r="D47" s="31"/>
+      <c r="E47" s="31"/>
+      <c r="F47" s="31"/>
+      <c r="G47" s="31"/>
+      <c r="H47" s="31"/>
+      <c r="I47" s="31"/>
+      <c r="J47" s="31"/>
+      <c r="K47" s="31"/>
+      <c r="L47" s="31"/>
+      <c r="M47" s="31"/>
+      <c r="N47" s="31"/>
+      <c r="O47" s="31"/>
+      <c r="P47" s="31"/>
     </row>
     <row r="48" spans="1:16" ht="34" x14ac:dyDescent="0.2">
       <c r="A48" s="2" t="s">
@@ -59979,7 +59979,7 @@
       <c r="C1" s="25" t="s">
         <v>50</v>
       </c>
-      <c r="D1" s="31" t="s">
+      <c r="D1" s="29" t="s">
         <v>58</v>
       </c>
     </row>

--- a/HelloFresh_Absorption.xlsx
+++ b/HelloFresh_Absorption.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://nuwildcat-my.sharepoint.com/personal/stn424_ads_northwestern_edu/Documents/Collaborations/Proposals/GO-Barrier, TFMI Proposals with Tim Wei/URAP_2023-10/Shared/Lanning, Mackenzie/graphene-oxide-paper-coatings/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2134" documentId="13_ncr:1_{F2E763B4-4DB6-894B-B240-8188D6068E1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{86EF033D-2D68-2D4E-9CB9-4B2F3C23BAA6}"/>
+  <xr:revisionPtr revIDLastSave="2137" documentId="13_ncr:1_{F2E763B4-4DB6-894B-B240-8188D6068E1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2C212AA3-8458-BB4F-A73B-0556EC749CA9}"/>
   <bookViews>
-    <workbookView xWindow="13980" yWindow="740" windowWidth="15420" windowHeight="17180" firstSheet="2" activeTab="6" xr2:uid="{304DC28A-0BB6-064B-B35E-217EA1A1C90F}"/>
+    <workbookView xWindow="13980" yWindow="740" windowWidth="15420" windowHeight="17180" firstSheet="1" activeTab="2" xr2:uid="{304DC28A-0BB6-064B-B35E-217EA1A1C90F}"/>
   </bookViews>
   <sheets>
     <sheet name="Crayola Method" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1239" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1240" uniqueCount="60">
   <si>
     <t>Raw Weights (gms)</t>
   </si>
@@ -219,6 +219,9 @@
   </si>
   <si>
     <t xml:space="preserve">Absorption </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> a.      </t>
   </si>
 </sst>
 </file>
@@ -42984,7 +42987,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{52A2020B-8186-F84C-A299-01D2941B7A3F}">
-  <dimension ref="A1:R160"/>
+  <dimension ref="A1:T160"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="11" max="11" width="12.83203125" customWidth="1"/>
@@ -44870,6 +44873,7 @@
       <c r="D46" s="6"/>
       <c r="E46" s="6"/>
       <c r="F46" s="10"/>
+      <c r="Q46" s="24"/>
       <c r="R46" s="6"/>
     </row>
     <row r="47" spans="1:18" x14ac:dyDescent="0.2">
@@ -48559,7 +48563,7 @@
       <c r="H128" s="2"/>
       <c r="R128" s="2"/>
     </row>
-    <row r="129" spans="1:18" ht="51" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:20" ht="51" x14ac:dyDescent="0.2">
       <c r="A129" s="2"/>
       <c r="B129" s="3" t="s">
         <v>2</v>
@@ -48608,7 +48612,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="130" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A130" s="4"/>
       <c r="B130" s="5">
         <v>0</v>
@@ -48671,7 +48675,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="131" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A131" s="4"/>
       <c r="B131" s="5">
         <v>10</v>
@@ -48734,7 +48738,7 @@
         <v>0.13836403442827419</v>
       </c>
     </row>
-    <row r="132" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A132" s="4"/>
       <c r="B132" s="5">
         <v>20</v>
@@ -48797,7 +48801,7 @@
         <v>0.21103594568585438</v>
       </c>
     </row>
-    <row r="133" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A133" s="4"/>
       <c r="B133" s="5">
         <v>30</v>
@@ -48860,7 +48864,7 @@
         <v>0.23731279495413199</v>
       </c>
     </row>
-    <row r="134" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A134" s="4"/>
       <c r="B134" s="5">
         <v>40</v>
@@ -48923,7 +48927,7 @@
         <v>0.24470315881083501</v>
       </c>
     </row>
-    <row r="135" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A135" s="4"/>
       <c r="B135" s="5">
         <v>50</v>
@@ -48986,7 +48990,7 @@
         <v>0.25086179535808761</v>
       </c>
     </row>
-    <row r="136" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A136" s="4"/>
       <c r="B136" s="5">
         <v>60</v>
@@ -49048,8 +49052,11 @@
         <f t="shared" si="237"/>
         <v>0.25250409843735494</v>
       </c>
-    </row>
-    <row r="137" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="T136" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="137" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A137" s="4"/>
       <c r="B137" s="5"/>
       <c r="C137" s="7"/>
@@ -49060,7 +49067,7 @@
       <c r="H137" s="7"/>
       <c r="R137" s="7"/>
     </row>
-    <row r="138" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A138" s="4"/>
       <c r="B138" s="5"/>
       <c r="C138" s="5"/>
@@ -49070,7 +49077,7 @@
       <c r="H138" s="4"/>
       <c r="R138" s="5"/>
     </row>
-    <row r="139" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A139" s="4"/>
       <c r="B139" s="5"/>
       <c r="C139" s="5"/>
@@ -49081,7 +49088,7 @@
       <c r="H139" s="4"/>
       <c r="R139" s="5"/>
     </row>
-    <row r="140" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A140" s="8" t="s">
         <v>14</v>
       </c>
@@ -49094,7 +49101,7 @@
       <c r="H140" s="2"/>
       <c r="R140" s="13"/>
     </row>
-    <row r="141" spans="1:18" ht="51" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:20" ht="51" x14ac:dyDescent="0.2">
       <c r="A141" s="2"/>
       <c r="B141" s="3" t="s">
         <v>2</v>
@@ -49143,7 +49150,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="142" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A142" s="4"/>
       <c r="B142" s="5">
         <v>0</v>
@@ -49206,7 +49213,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="143" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A143" s="4"/>
       <c r="B143" s="5">
         <v>10</v>
@@ -49269,7 +49276,7 @@
         <v>5.7661530307589123E-3</v>
       </c>
     </row>
-    <row r="144" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A144" s="4"/>
       <c r="B144" s="5">
         <v>20</v>
